--- a/12-06-2026-vokab/nyheder.xlsx
+++ b/12-06-2026-vokab/nyheder.xlsx
@@ -123,10 +123,10 @@
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Jpan" typeface="ï¼­ï¼³ ï¼°ã´ã·ãã¯"/>
+        <a:font script="Hang" typeface="ë§ì ê³ ë"/>
+        <a:font script="Hans" typeface="å®ä½"/>
+        <a:font script="Hant" typeface="æ°ç´°æé«"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
         <a:font script="Thai" typeface="Tahoma"/>
@@ -158,10 +158,10 @@
         <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Jpan" typeface="ï¼­ï¼³ ï¼°ã´ã·ãã¯"/>
+        <a:font script="Hang" typeface="ë§ì ê³ ë"/>
+        <a:font script="Hans" typeface="å®ä½"/>
+        <a:font script="Hant" typeface="æ°ç´°æé«"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
         <a:font script="Thai" typeface="Tahoma"/>
@@ -399,7 +399,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:V2"/>
+  <dimension ref="A1:W2"/>
   <cols>
     <col min="1" max="1" width="10.83203125" customWidth="1"/>
     <col min="2" max="2" width="11.83203125" customWidth="1"/>
@@ -423,6 +423,7 @@
     <col min="20" max="20" width="7.83203125" customWidth="1" hidden="true"/>
     <col min="21" max="21" width="6.83203125" customWidth="1" hidden="true"/>
     <col min="22" max="22" width="7.83203125" customWidth="1" hidden="true"/>
+    <col min="23" max="23" width="40.83203125" customWidth="1" hidden="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -492,6 +493,9 @@
       <c r="V1" t="str">
         <v>Lapses</v>
       </c>
+      <c r="W1" t="str">
+        <v>Candidates</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
@@ -504,10 +508,10 @@
         <v>tværs</v>
       </c>
       <c r="D2" t="str">
-        <v/>
+        <v>tværs</v>
       </c>
       <c r="E2" t="str">
-        <v/>
+        <v>adverbium</v>
       </c>
       <c r="F2" t="str">
         <v/>
@@ -516,13 +520,13 @@
         <v/>
       </c>
       <c r="H2" t="str">
-        <v/>
+        <v>[ˈtvæɐ̯s]</v>
       </c>
       <c r="I2" t="str">
-        <v/>
+        <v>https://static.ordnet.dk/mp3/12003/12003082_1.mp3</v>
       </c>
       <c r="J2" t="str">
-        <v/>
+        <v>i en retning der (vinkelret) krydser en længderetning</v>
       </c>
       <c r="K2" t="str">
         <v>cross</v>
@@ -543,7 +547,7 @@
         <v/>
       </c>
       <c r="Q2" t="str">
-        <v>pending</v>
+        <v>ok</v>
       </c>
       <c r="R2" t="str">
         <v/>
@@ -558,19 +562,22 @@
         <v/>
       </c>
       <c r="V2" t="str">
+        <v/>
+      </c>
+      <c r="W2" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:V2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:W2"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P1"/>
+  <dimension ref="A1:Q1"/>
   <cols>
     <col min="1" max="1" width="10.83203125" customWidth="1"/>
     <col min="2" max="2" width="11.83203125" customWidth="1"/>
@@ -588,6 +595,7 @@
     <col min="14" max="14" width="7.83203125" customWidth="1" hidden="true"/>
     <col min="15" max="15" width="6.83203125" customWidth="1" hidden="true"/>
     <col min="16" max="16" width="7.83203125" customWidth="1" hidden="true"/>
+    <col min="17" max="17" width="40.83203125" customWidth="1" hidden="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -639,10 +647,13 @@
       <c r="P1" t="str">
         <v>Lapses</v>
       </c>
+      <c r="Q1" t="str">
+        <v>Candidates</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:P1"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:Q1"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -651,8 +662,8 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:B4"/>
   <cols>
-    <col min="1" max="1" width="16.83203125" customWidth="1"/>
-    <col min="2" max="2" width="28.83203125" customWidth="1"/>
+    <col min="1" max="1" customWidth="1" width="16.83203125"/>
+    <col min="2" max="2" customWidth="1" width="28.83203125"/>
   </cols>
   <sheetData>
     <row r="1">

--- a/12-06-2026-vokab/nyheder.xlsx
+++ b/12-06-2026-vokab/nyheder.xlsx
@@ -123,10 +123,10 @@
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ï¼­ï¼³ ï¼°ã´ã·ãã¯"/>
-        <a:font script="Hang" typeface="ë§ì ê³ ë"/>
-        <a:font script="Hans" typeface="å®ä½"/>
-        <a:font script="Hant" typeface="æ°ç´°æé«"/>
+        <a:font script="Jpan" typeface="Ã¯Â¼Â­Ã¯Â¼Â³ Ã¯Â¼Â°Ã£ÂÂ´Ã£ÂÂ·Ã£ÂÂÃ£ÂÂ¯"/>
+        <a:font script="Hang" typeface="Ã«Â§ÂÃ¬ÂÂ ÃªÂ³Â Ã«ÂÂ"/>
+        <a:font script="Hans" typeface="Ã¥Â®ÂÃ¤Â½Â"/>
+        <a:font script="Hant" typeface="Ã¦ÂÂ°Ã§Â´Â°Ã¦ÂÂÃ©Â«Â"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
         <a:font script="Thai" typeface="Tahoma"/>
@@ -158,10 +158,10 @@
         <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ï¼­ï¼³ ï¼°ã´ã·ãã¯"/>
-        <a:font script="Hang" typeface="ë§ì ê³ ë"/>
-        <a:font script="Hans" typeface="å®ä½"/>
-        <a:font script="Hant" typeface="æ°ç´°æé«"/>
+        <a:font script="Jpan" typeface="Ã¯Â¼Â­Ã¯Â¼Â³ Ã¯Â¼Â°Ã£ÂÂ´Ã£ÂÂ·Ã£ÂÂÃ£ÂÂ¯"/>
+        <a:font script="Hang" typeface="Ã«Â§ÂÃ¬ÂÂ ÃªÂ³Â Ã«ÂÂ"/>
+        <a:font script="Hans" typeface="Ã¥Â®ÂÃ¤Â½Â"/>
+        <a:font script="Hant" typeface="Ã¦ÂÂ°Ã§Â´Â°Ã¦ÂÂÃ©Â«Â"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
         <a:font script="Thai" typeface="Tahoma"/>
@@ -401,29 +401,29 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:W2"/>
   <cols>
-    <col min="1" max="1" width="10.83203125" customWidth="1"/>
-    <col min="2" max="2" width="11.83203125" customWidth="1"/>
-    <col min="3" max="3" width="18.83203125" customWidth="1"/>
-    <col min="4" max="4" width="14.83203125" customWidth="1"/>
-    <col min="5" max="5" width="11.83203125" customWidth="1"/>
-    <col min="6" max="6" width="8.83203125" customWidth="1"/>
-    <col min="7" max="7" width="26.83203125" customWidth="1"/>
-    <col min="8" max="8" width="16.83203125" customWidth="1"/>
-    <col min="9" max="9" width="18.83203125" customWidth="1"/>
-    <col min="10" max="10" width="36.83203125" customWidth="1"/>
-    <col min="11" max="11" width="36.83203125" customWidth="1"/>
-    <col min="12" max="12" width="50.83203125" customWidth="1"/>
-    <col min="13" max="13" width="24.83203125" customWidth="1"/>
-    <col min="14" max="14" width="24.83203125" customWidth="1"/>
-    <col min="15" max="15" width="24.83203125" customWidth="1"/>
-    <col min="16" max="16" width="18.83203125" customWidth="1"/>
-    <col min="17" max="17" width="10.83203125" customWidth="1"/>
-    <col min="18" max="18" width="11.83203125" customWidth="1" hidden="true"/>
-    <col min="19" max="19" width="9.83203125" customWidth="1" hidden="true"/>
-    <col min="20" max="20" width="7.83203125" customWidth="1" hidden="true"/>
-    <col min="21" max="21" width="6.83203125" customWidth="1" hidden="true"/>
-    <col min="22" max="22" width="7.83203125" customWidth="1" hidden="true"/>
-    <col min="23" max="23" width="40.83203125" customWidth="1" hidden="true"/>
+    <col min="1" max="1" customWidth="1" width="10.83203125"/>
+    <col min="2" max="2" customWidth="1" width="11.83203125"/>
+    <col min="3" max="3" customWidth="1" width="18.83203125"/>
+    <col min="4" max="4" customWidth="1" width="14.83203125"/>
+    <col min="5" max="5" customWidth="1" width="11.83203125"/>
+    <col min="6" max="6" customWidth="1" width="8.83203125"/>
+    <col min="7" max="7" customWidth="1" width="26.83203125"/>
+    <col min="8" max="8" customWidth="1" width="16.83203125"/>
+    <col min="9" max="9" customWidth="1" width="18.83203125"/>
+    <col min="10" max="10" customWidth="1" width="36.83203125"/>
+    <col min="11" max="11" customWidth="1" width="36.83203125"/>
+    <col min="12" max="12" customWidth="1" width="50.83203125"/>
+    <col min="13" max="13" customWidth="1" width="24.83203125"/>
+    <col min="14" max="14" customWidth="1" width="24.83203125"/>
+    <col min="15" max="15" customWidth="1" width="24.83203125"/>
+    <col min="16" max="16" customWidth="1" width="18.83203125"/>
+    <col min="17" max="17" customWidth="1" width="10.83203125"/>
+    <col min="18" max="18" customWidth="1" width="11.83203125" hidden="true"/>
+    <col min="19" max="19" customWidth="1" width="9.83203125" hidden="true"/>
+    <col min="20" max="20" customWidth="1" width="7.83203125" hidden="true"/>
+    <col min="21" max="21" customWidth="1" width="6.83203125" hidden="true"/>
+    <col min="22" max="22" customWidth="1" width="7.83203125" hidden="true"/>
+    <col min="23" max="23" customWidth="1" width="40.83203125" hidden="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -550,19 +550,19 @@
         <v>ok</v>
       </c>
       <c r="R2" t="str">
-        <v/>
+        <v>2026-06-17</v>
       </c>
       <c r="S2" t="str">
-        <v/>
+        <v>0</v>
       </c>
       <c r="T2" t="str">
-        <v/>
+        <v>2.3</v>
       </c>
       <c r="U2" t="str">
-        <v/>
+        <v>0</v>
       </c>
       <c r="V2" t="str">
-        <v/>
+        <v>0</v>
       </c>
       <c r="W2" t="str">
         <v/>
@@ -579,23 +579,23 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:Q1"/>
   <cols>
-    <col min="1" max="1" width="10.83203125" customWidth="1"/>
-    <col min="2" max="2" width="11.83203125" customWidth="1"/>
-    <col min="3" max="3" width="30.83203125" customWidth="1"/>
-    <col min="4" max="4" width="36.83203125" customWidth="1"/>
-    <col min="5" max="5" width="36.83203125" customWidth="1"/>
-    <col min="6" max="6" width="50.83203125" customWidth="1"/>
-    <col min="7" max="7" width="24.83203125" customWidth="1"/>
-    <col min="8" max="8" width="24.83203125" customWidth="1"/>
-    <col min="9" max="9" width="24.83203125" customWidth="1"/>
-    <col min="10" max="10" width="18.83203125" customWidth="1"/>
-    <col min="11" max="11" width="10.83203125" customWidth="1"/>
-    <col min="12" max="12" width="11.83203125" customWidth="1" hidden="true"/>
-    <col min="13" max="13" width="9.83203125" customWidth="1" hidden="true"/>
-    <col min="14" max="14" width="7.83203125" customWidth="1" hidden="true"/>
-    <col min="15" max="15" width="6.83203125" customWidth="1" hidden="true"/>
-    <col min="16" max="16" width="7.83203125" customWidth="1" hidden="true"/>
-    <col min="17" max="17" width="40.83203125" customWidth="1" hidden="true"/>
+    <col min="1" max="1" customWidth="1" width="10.83203125"/>
+    <col min="2" max="2" customWidth="1" width="11.83203125"/>
+    <col min="3" max="3" customWidth="1" width="30.83203125"/>
+    <col min="4" max="4" customWidth="1" width="36.83203125"/>
+    <col min="5" max="5" customWidth="1" width="36.83203125"/>
+    <col min="6" max="6" customWidth="1" width="50.83203125"/>
+    <col min="7" max="7" customWidth="1" width="24.83203125"/>
+    <col min="8" max="8" customWidth="1" width="24.83203125"/>
+    <col min="9" max="9" customWidth="1" width="24.83203125"/>
+    <col min="10" max="10" customWidth="1" width="18.83203125"/>
+    <col min="11" max="11" customWidth="1" width="10.83203125"/>
+    <col min="12" max="12" customWidth="1" width="11.83203125" hidden="true"/>
+    <col min="13" max="13" customWidth="1" width="9.83203125" hidden="true"/>
+    <col min="14" max="14" customWidth="1" width="7.83203125" hidden="true"/>
+    <col min="15" max="15" customWidth="1" width="6.83203125" hidden="true"/>
+    <col min="16" max="16" customWidth="1" width="7.83203125" hidden="true"/>
+    <col min="17" max="17" customWidth="1" width="40.83203125" hidden="true"/>
   </cols>
   <sheetData>
     <row r="1">

--- a/12-06-2026-vokab/nyheder.xlsx
+++ b/12-06-2026-vokab/nyheder.xlsx
@@ -123,10 +123,10 @@
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="Ã¯Â¼Â­Ã¯Â¼Â³ Ã¯Â¼Â°Ã£ÂÂ´Ã£ÂÂ·Ã£ÂÂÃ£ÂÂ¯"/>
-        <a:font script="Hang" typeface="Ã«Â§ÂÃ¬ÂÂ ÃªÂ³Â Ã«ÂÂ"/>
-        <a:font script="Hans" typeface="Ã¥Â®ÂÃ¤Â½Â"/>
-        <a:font script="Hant" typeface="Ã¦ÂÂ°Ã§Â´Â°Ã¦ÂÂÃ©Â«Â"/>
+        <a:font script="Jpan" typeface="ÃÂ¯ÃÂ¼ÃÂ­ÃÂ¯ÃÂ¼ÃÂ³ ÃÂ¯ÃÂ¼ÃÂ°ÃÂ£ÃÂÃÂ´ÃÂ£ÃÂÃÂ·ÃÂ£ÃÂÃÂÃÂ£ÃÂÃÂ¯"/>
+        <a:font script="Hang" typeface="ÃÂ«ÃÂ§ÃÂÃÂ¬ÃÂÃÂ ÃÂªÃÂ³ÃÂ ÃÂ«ÃÂÃÂ"/>
+        <a:font script="Hans" typeface="ÃÂ¥ÃÂ®ÃÂÃÂ¤ÃÂ½ÃÂ"/>
+        <a:font script="Hant" typeface="ÃÂ¦ÃÂÃÂ°ÃÂ§ÃÂ´ÃÂ°ÃÂ¦ÃÂÃÂÃÂ©ÃÂ«ÃÂ"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
         <a:font script="Thai" typeface="Tahoma"/>
@@ -158,10 +158,10 @@
         <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="Ã¯Â¼Â­Ã¯Â¼Â³ Ã¯Â¼Â°Ã£ÂÂ´Ã£ÂÂ·Ã£ÂÂÃ£ÂÂ¯"/>
-        <a:font script="Hang" typeface="Ã«Â§ÂÃ¬ÂÂ ÃªÂ³Â Ã«ÂÂ"/>
-        <a:font script="Hans" typeface="Ã¥Â®ÂÃ¤Â½Â"/>
-        <a:font script="Hant" typeface="Ã¦ÂÂ°Ã§Â´Â°Ã¦ÂÂÃ©Â«Â"/>
+        <a:font script="Jpan" typeface="ÃÂ¯ÃÂ¼ÃÂ­ÃÂ¯ÃÂ¼ÃÂ³ ÃÂ¯ÃÂ¼ÃÂ°ÃÂ£ÃÂÃÂ´ÃÂ£ÃÂÃÂ·ÃÂ£ÃÂÃÂÃÂ£ÃÂÃÂ¯"/>
+        <a:font script="Hang" typeface="ÃÂ«ÃÂ§ÃÂÃÂ¬ÃÂÃÂ ÃÂªÃÂ³ÃÂ ÃÂ«ÃÂÃÂ"/>
+        <a:font script="Hans" typeface="ÃÂ¥ÃÂ®ÃÂÃÂ¤ÃÂ½ÃÂ"/>
+        <a:font script="Hant" typeface="ÃÂ¦ÃÂÃÂ°ÃÂ§ÃÂ´ÃÂ°ÃÂ¦ÃÂÃÂÃÂ©ÃÂ«ÃÂ"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
         <a:font script="Thai" typeface="Tahoma"/>
@@ -550,16 +550,16 @@
         <v>ok</v>
       </c>
       <c r="R2" t="str">
-        <v>2026-06-17</v>
+        <v>2026-06-18</v>
       </c>
       <c r="S2" t="str">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T2" t="str">
         <v>2.3</v>
       </c>
       <c r="U2" t="str">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V2" t="str">
         <v>0</v>

--- a/12-06-2026-vokab/nyheder.xlsx
+++ b/12-06-2026-vokab/nyheder.xlsx
@@ -123,10 +123,10 @@
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ÃÂ¯ÃÂ¼ÃÂ­ÃÂ¯ÃÂ¼ÃÂ³ ÃÂ¯ÃÂ¼ÃÂ°ÃÂ£ÃÂÃÂ´ÃÂ£ÃÂÃÂ·ÃÂ£ÃÂÃÂÃÂ£ÃÂÃÂ¯"/>
-        <a:font script="Hang" typeface="ÃÂ«ÃÂ§ÃÂÃÂ¬ÃÂÃÂ ÃÂªÃÂ³ÃÂ ÃÂ«ÃÂÃÂ"/>
-        <a:font script="Hans" typeface="ÃÂ¥ÃÂ®ÃÂÃÂ¤ÃÂ½ÃÂ"/>
-        <a:font script="Hant" typeface="ÃÂ¦ÃÂÃÂ°ÃÂ§ÃÂ´ÃÂ°ÃÂ¦ÃÂÃÂÃÂ©ÃÂ«ÃÂ"/>
+        <a:font script="Jpan" typeface="ÃÂÃÂ¯ÃÂÃÂ¼ÃÂÃÂ­ÃÂÃÂ¯ÃÂÃÂ¼ÃÂÃÂ³ ÃÂÃÂ¯ÃÂÃÂ¼ÃÂÃÂ°ÃÂÃÂ£ÃÂÃÂÃÂÃÂ´ÃÂÃÂ£ÃÂÃÂÃÂÃÂ·ÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂ¯"/>
+        <a:font script="Hang" typeface="ÃÂÃÂ«ÃÂÃÂ§ÃÂÃÂÃÂÃÂ¬ÃÂÃÂÃÂÃÂ ÃÂÃÂªÃÂÃÂ³ÃÂÃÂ ÃÂÃÂ«ÃÂÃÂÃÂÃÂ"/>
+        <a:font script="Hans" typeface="ÃÂÃÂ¥ÃÂÃÂ®ÃÂÃÂÃÂÃÂ¤ÃÂÃÂ½ÃÂÃÂ"/>
+        <a:font script="Hant" typeface="ÃÂÃÂ¦ÃÂÃÂÃÂÃÂ°ÃÂÃÂ§ÃÂÃÂ´ÃÂÃÂ°ÃÂÃÂ¦ÃÂÃÂÃÂÃÂÃÂÃÂ©ÃÂÃÂ«ÃÂÃÂ"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
         <a:font script="Thai" typeface="Tahoma"/>
@@ -158,10 +158,10 @@
         <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ÃÂ¯ÃÂ¼ÃÂ­ÃÂ¯ÃÂ¼ÃÂ³ ÃÂ¯ÃÂ¼ÃÂ°ÃÂ£ÃÂÃÂ´ÃÂ£ÃÂÃÂ·ÃÂ£ÃÂÃÂÃÂ£ÃÂÃÂ¯"/>
-        <a:font script="Hang" typeface="ÃÂ«ÃÂ§ÃÂÃÂ¬ÃÂÃÂ ÃÂªÃÂ³ÃÂ ÃÂ«ÃÂÃÂ"/>
-        <a:font script="Hans" typeface="ÃÂ¥ÃÂ®ÃÂÃÂ¤ÃÂ½ÃÂ"/>
-        <a:font script="Hant" typeface="ÃÂ¦ÃÂÃÂ°ÃÂ§ÃÂ´ÃÂ°ÃÂ¦ÃÂÃÂÃÂ©ÃÂ«ÃÂ"/>
+        <a:font script="Jpan" typeface="ÃÂÃÂ¯ÃÂÃÂ¼ÃÂÃÂ­ÃÂÃÂ¯ÃÂÃÂ¼ÃÂÃÂ³ ÃÂÃÂ¯ÃÂÃÂ¼ÃÂÃÂ°ÃÂÃÂ£ÃÂÃÂÃÂÃÂ´ÃÂÃÂ£ÃÂÃÂÃÂÃÂ·ÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂ¯"/>
+        <a:font script="Hang" typeface="ÃÂÃÂ«ÃÂÃÂ§ÃÂÃÂÃÂÃÂ¬ÃÂÃÂÃÂÃÂ ÃÂÃÂªÃÂÃÂ³ÃÂÃÂ ÃÂÃÂ«ÃÂÃÂÃÂÃÂ"/>
+        <a:font script="Hans" typeface="ÃÂÃÂ¥ÃÂÃÂ®ÃÂÃÂÃÂÃÂ¤ÃÂÃÂ½ÃÂÃÂ"/>
+        <a:font script="Hant" typeface="ÃÂÃÂ¦ÃÂÃÂÃÂÃÂ°ÃÂÃÂ§ÃÂÃÂ´ÃÂÃÂ°ÃÂÃÂ¦ÃÂÃÂÃÂÃÂÃÂÃÂ©ÃÂÃÂ«ÃÂÃÂ"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
         <a:font script="Thai" typeface="Tahoma"/>
@@ -553,16 +553,16 @@
         <v>2026-06-18</v>
       </c>
       <c r="S2" t="str">
+        <v>0</v>
+      </c>
+      <c r="T2" t="str">
+        <v>2.1</v>
+      </c>
+      <c r="U2" t="str">
+        <v>0</v>
+      </c>
+      <c r="V2" t="str">
         <v>1</v>
-      </c>
-      <c r="T2" t="str">
-        <v>2.3</v>
-      </c>
-      <c r="U2" t="str">
-        <v>1</v>
-      </c>
-      <c r="V2" t="str">
-        <v>0</v>
       </c>
       <c r="W2" t="str">
         <v/>

--- a/12-06-2026-vokab/nyheder.xlsx
+++ b/12-06-2026-vokab/nyheder.xlsx
@@ -123,10 +123,10 @@
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ÃÂÃÂ¯ÃÂÃÂ¼ÃÂÃÂ­ÃÂÃÂ¯ÃÂÃÂ¼ÃÂÃÂ³ ÃÂÃÂ¯ÃÂÃÂ¼ÃÂÃÂ°ÃÂÃÂ£ÃÂÃÂÃÂÃÂ´ÃÂÃÂ£ÃÂÃÂÃÂÃÂ·ÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂ¯"/>
-        <a:font script="Hang" typeface="ÃÂÃÂ«ÃÂÃÂ§ÃÂÃÂÃÂÃÂ¬ÃÂÃÂÃÂÃÂ ÃÂÃÂªÃÂÃÂ³ÃÂÃÂ ÃÂÃÂ«ÃÂÃÂÃÂÃÂ"/>
-        <a:font script="Hans" typeface="ÃÂÃÂ¥ÃÂÃÂ®ÃÂÃÂÃÂÃÂ¤ÃÂÃÂ½ÃÂÃÂ"/>
-        <a:font script="Hant" typeface="ÃÂÃÂ¦ÃÂÃÂÃÂÃÂ°ÃÂÃÂ§ÃÂÃÂ´ÃÂÃÂ°ÃÂÃÂ¦ÃÂÃÂÃÂÃÂÃÂÃÂ©ÃÂÃÂ«ÃÂÃÂ"/>
+        <a:font script="Jpan" typeface="ÃÂÃÂÃÂÃÂ¯ÃÂÃÂÃÂÃÂ¼ÃÂÃÂÃÂÃÂ­ÃÂÃÂÃÂÃÂ¯ÃÂÃÂÃÂÃÂ¼ÃÂÃÂÃÂÃÂ³ ÃÂÃÂÃÂÃÂ¯ÃÂÃÂÃÂÃÂ¼ÃÂÃÂÃÂÃÂ°ÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ´ÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ·ÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¯"/>
+        <a:font script="Hang" typeface="ÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¬ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ ÃÂÃÂÃÂÃÂªÃÂÃÂÃÂÃÂ³ÃÂÃÂÃÂÃÂ ÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ"/>
+        <a:font script="Hans" typeface="ÃÂÃÂÃÂÃÂ¥ÃÂÃÂÃÂÃÂ®ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¤ÃÂÃÂÃÂÃÂ½ÃÂÃÂÃÂÃÂ"/>
+        <a:font script="Hant" typeface="ÃÂÃÂÃÂÃÂ¦ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ°ÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂ´ÃÂÃÂÃÂÃÂ°ÃÂÃÂÃÂÃÂ¦ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ©ÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂ"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
         <a:font script="Thai" typeface="Tahoma"/>
@@ -158,10 +158,10 @@
         <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ÃÂÃÂ¯ÃÂÃÂ¼ÃÂÃÂ­ÃÂÃÂ¯ÃÂÃÂ¼ÃÂÃÂ³ ÃÂÃÂ¯ÃÂÃÂ¼ÃÂÃÂ°ÃÂÃÂ£ÃÂÃÂÃÂÃÂ´ÃÂÃÂ£ÃÂÃÂÃÂÃÂ·ÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂ¯"/>
-        <a:font script="Hang" typeface="ÃÂÃÂ«ÃÂÃÂ§ÃÂÃÂÃÂÃÂ¬ÃÂÃÂÃÂÃÂ ÃÂÃÂªÃÂÃÂ³ÃÂÃÂ ÃÂÃÂ«ÃÂÃÂÃÂÃÂ"/>
-        <a:font script="Hans" typeface="ÃÂÃÂ¥ÃÂÃÂ®ÃÂÃÂÃÂÃÂ¤ÃÂÃÂ½ÃÂÃÂ"/>
-        <a:font script="Hant" typeface="ÃÂÃÂ¦ÃÂÃÂÃÂÃÂ°ÃÂÃÂ§ÃÂÃÂ´ÃÂÃÂ°ÃÂÃÂ¦ÃÂÃÂÃÂÃÂÃÂÃÂ©ÃÂÃÂ«ÃÂÃÂ"/>
+        <a:font script="Jpan" typeface="ÃÂÃÂÃÂÃÂ¯ÃÂÃÂÃÂÃÂ¼ÃÂÃÂÃÂÃÂ­ÃÂÃÂÃÂÃÂ¯ÃÂÃÂÃÂÃÂ¼ÃÂÃÂÃÂÃÂ³ ÃÂÃÂÃÂÃÂ¯ÃÂÃÂÃÂÃÂ¼ÃÂÃÂÃÂÃÂ°ÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ´ÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ·ÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¯"/>
+        <a:font script="Hang" typeface="ÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¬ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ ÃÂÃÂÃÂÃÂªÃÂÃÂÃÂÃÂ³ÃÂÃÂÃÂÃÂ ÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ"/>
+        <a:font script="Hans" typeface="ÃÂÃÂÃÂÃÂ¥ÃÂÃÂÃÂÃÂ®ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¤ÃÂÃÂÃÂÃÂ½ÃÂÃÂÃÂÃÂ"/>
+        <a:font script="Hant" typeface="ÃÂÃÂÃÂÃÂ¦ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ°ÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂ´ÃÂÃÂÃÂÃÂ°ÃÂÃÂÃÂÃÂ¦ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ©ÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂ"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
         <a:font script="Thai" typeface="Tahoma"/>
@@ -399,31 +399,31 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:W2"/>
+  <dimension ref="A1:W3"/>
   <cols>
-    <col min="1" max="1" customWidth="1" width="10.83203125"/>
-    <col min="2" max="2" customWidth="1" width="11.83203125"/>
-    <col min="3" max="3" customWidth="1" width="18.83203125"/>
-    <col min="4" max="4" customWidth="1" width="14.83203125"/>
-    <col min="5" max="5" customWidth="1" width="11.83203125"/>
-    <col min="6" max="6" customWidth="1" width="8.83203125"/>
-    <col min="7" max="7" customWidth="1" width="26.83203125"/>
-    <col min="8" max="8" customWidth="1" width="16.83203125"/>
-    <col min="9" max="9" customWidth="1" width="18.83203125"/>
-    <col min="10" max="10" customWidth="1" width="36.83203125"/>
-    <col min="11" max="11" customWidth="1" width="36.83203125"/>
-    <col min="12" max="12" customWidth="1" width="50.83203125"/>
-    <col min="13" max="13" customWidth="1" width="24.83203125"/>
-    <col min="14" max="14" customWidth="1" width="24.83203125"/>
-    <col min="15" max="15" customWidth="1" width="24.83203125"/>
-    <col min="16" max="16" customWidth="1" width="18.83203125"/>
-    <col min="17" max="17" customWidth="1" width="10.83203125"/>
-    <col min="18" max="18" customWidth="1" width="11.83203125" hidden="true"/>
-    <col min="19" max="19" customWidth="1" width="9.83203125" hidden="true"/>
-    <col min="20" max="20" customWidth="1" width="7.83203125" hidden="true"/>
-    <col min="21" max="21" customWidth="1" width="6.83203125" hidden="true"/>
-    <col min="22" max="22" customWidth="1" width="7.83203125" hidden="true"/>
-    <col min="23" max="23" customWidth="1" width="40.83203125" hidden="true"/>
+    <col min="1" max="1" width="10.83203125" customWidth="1"/>
+    <col min="2" max="2" width="11.83203125" customWidth="1"/>
+    <col min="3" max="3" width="18.83203125" customWidth="1"/>
+    <col min="4" max="4" width="14.83203125" customWidth="1"/>
+    <col min="5" max="5" width="11.83203125" customWidth="1"/>
+    <col min="6" max="6" width="8.83203125" customWidth="1"/>
+    <col min="7" max="7" width="26.83203125" customWidth="1"/>
+    <col min="8" max="8" width="16.83203125" customWidth="1"/>
+    <col min="9" max="9" width="18.83203125" customWidth="1"/>
+    <col min="10" max="10" width="36.83203125" customWidth="1"/>
+    <col min="11" max="11" width="36.83203125" customWidth="1"/>
+    <col min="12" max="12" width="50.83203125" customWidth="1"/>
+    <col min="13" max="13" width="24.83203125" customWidth="1"/>
+    <col min="14" max="14" width="24.83203125" customWidth="1"/>
+    <col min="15" max="15" width="24.83203125" customWidth="1"/>
+    <col min="16" max="16" width="18.83203125" customWidth="1"/>
+    <col min="17" max="17" width="10.83203125" customWidth="1"/>
+    <col min="18" max="18" width="11.83203125" customWidth="1" hidden="true"/>
+    <col min="19" max="19" width="9.83203125" customWidth="1" hidden="true"/>
+    <col min="20" max="20" width="7.83203125" customWidth="1" hidden="true"/>
+    <col min="21" max="21" width="6.83203125" customWidth="1" hidden="true"/>
+    <col min="22" max="22" width="7.83203125" customWidth="1" hidden="true"/>
+    <col min="23" max="23" width="40.83203125" customWidth="1" hidden="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -568,9 +568,80 @@
         <v/>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>17fb1307-5e2d-4c40-a700-5c78bc02759d</v>
+      </c>
+      <c r="B3" t="str">
+        <v>2026-06-19</v>
+      </c>
+      <c r="C3" t="str">
+        <v>bekræfter</v>
+      </c>
+      <c r="D3" t="str">
+        <v>bekræfte</v>
+      </c>
+      <c r="E3" t="str">
+        <v>verbum</v>
+      </c>
+      <c r="F3" t="str">
+        <v/>
+      </c>
+      <c r="G3" t="str">
+        <v>-r, -de, -t</v>
+      </c>
+      <c r="H3" t="str">
+        <v>[beˈkʁafdə]</v>
+      </c>
+      <c r="I3" t="str">
+        <v>https://static.ordnet.dk/mp3/11003/11003976_1.mp3</v>
+      </c>
+      <c r="J3" t="str">
+        <v>bevidne rigtigheden af</v>
+      </c>
+      <c r="K3" t="str">
+        <v>confirms</v>
+      </c>
+      <c r="L3" t="str">
+        <v>Dansk minister bekræfter deltagelse i lukket Peter Thiel-netværk</v>
+      </c>
+      <c r="M3" t="str">
+        <v>Dansk minister bekræfter deltagelse i lukket Peter Thiel-netværk | Ingeniøren</v>
+      </c>
+      <c r="N3" t="str">
+        <v>https://ing.dk/artikel/dansk-minister-bekraefter-deltagelse-i-lukket-peter-thiel-netvaerk</v>
+      </c>
+      <c r="O3" t="str">
+        <v>https://ing.dk/artikel/dansk-minister-bekraefter-deltagelse-i-lukket-peter-thiel-netvaerk#:~:text=bekr%C3%A6fter</v>
+      </c>
+      <c r="P3" t="str">
+        <v/>
+      </c>
+      <c r="Q3" t="str">
+        <v>ok</v>
+      </c>
+      <c r="R3" t="str">
+        <v/>
+      </c>
+      <c r="S3" t="str">
+        <v/>
+      </c>
+      <c r="T3" t="str">
+        <v/>
+      </c>
+      <c r="U3" t="str">
+        <v/>
+      </c>
+      <c r="V3" t="str">
+        <v/>
+      </c>
+      <c r="W3" t="str">
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:W2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:W3"/>
   </ignoredErrors>
 </worksheet>
 </file>
